--- a/data/trans_bre/CAGE_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,45</t>
+          <t>-2,13; 0,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -4,45</t>
+          <t>-10,92; -4,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,43</t>
+          <t>-6,53; 0,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,89</t>
+          <t>-9,07; -0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -69,75</t>
+          <t>-100,0; -72,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 30,21</t>
+          <t>-86,22; 21,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,59</t>
+          <t>-2,85; -0,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -1,21</t>
+          <t>-4,25; -1,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,01</t>
+          <t>-1,9; 0,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,37; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 0,3</t>
+          <t>-6,78; 0,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,09</t>
+          <t>-93,24; 51,64</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,61</t>
+          <t>-2,88; 0,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,13; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-1,71; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,76</t>
+          <t>-2,97; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,2</t>
+          <t>-0,88; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,01</t>
+          <t>-6,31; -1,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,44</t>
+          <t>-3,55; -0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,16</t>
+          <t>-2,52; 1,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,69</t>
+          <t>-2,13; 0,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,27</t>
+          <t>-3,29; 3,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,97</t>
+          <t>-87,09; 279,82</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,14</t>
+          <t>-1,27; -0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,53</t>
+          <t>-3,08; -0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,38</t>
+          <t>-3,45; -0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,88</t>
+          <t>-4,77; 1,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,51</t>
+          <t>-100,0; -23,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-90,03; -1,28</t>
+          <t>-88,29; -1,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-94,56; 92,77</t>
+          <t>-95,44; 67,11</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,33</t>
+          <t>-0,87; 0,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,74; -0,54</t>
+          <t>-2,71; -0,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,26</t>
+          <t>-1,11; 0,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,18</t>
+          <t>-1,72; 3,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -28,02</t>
+          <t>-100,0; -20,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 175,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; -0,18</t>
+          <t>-0,86; -0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -1,31</t>
+          <t>-2,29; -1,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,5</t>
+          <t>-1,47; -0,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,27</t>
+          <t>-2,08; 0,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-86,85; -26,54</t>
+          <t>-86,05; -20,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-97,25; -81,54</t>
+          <t>-97,73; -82,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-81,91; -38,73</t>
+          <t>-82,48; -38,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 14,99</t>
+          <t>-76,01; 12,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/CAGE_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,45</t>
+          <t>-2,14; 0,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -4,45</t>
+          <t>-11,39; -4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 0,46</t>
+          <t>-6,34; 0,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -0,91</t>
+          <t>-6,88; -0,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -72,61</t>
+          <t>-100,0; -74,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,22; 21,77</t>
+          <t>-85,44; 26,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,57</t>
+          <t>-2,75; -0,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -1,09</t>
+          <t>-4,02; -1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,17</t>
+          <t>-1,73; 0,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-62,16%</t>
+          <t>-67,51%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,61; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,54</t>
+          <t>-8,22; -0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,24; 51,64</t>
+          <t>-100,0; 5,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,45%</t>
+          <t>-41,26%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,71</t>
+          <t>-2,82; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,0</t>
+          <t>-1,23; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,0</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,82</t>
+          <t>-2,15; 1,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,19</t>
+          <t>-0,88; 3,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,32</t>
+          <t>-5,8; -1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,44</t>
+          <t>-3,65; -0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-16,38%</t>
+          <t>-13,97%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,17</t>
+          <t>-2,22; 1,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-2,29; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,68</t>
+          <t>-1,84; 0,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,73</t>
+          <t>-3,57; 3,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 279,82</t>
+          <t>-100,0; 346,78</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-43,75%</t>
+          <t>0,09%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; -0,14</t>
+          <t>-1,25; -0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,55</t>
+          <t>-2,88; -0,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,4</t>
+          <t>-3,52; -0,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,45</t>
+          <t>-3,53; 4,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -23,07</t>
+          <t>-100,0; -20,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,29; -1,53</t>
+          <t>-89,74; -6,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-95,44; 67,11</t>
+          <t>-68,23; 166,52</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,35</t>
+          <t>-0,92; 0,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,51</t>
+          <t>-2,63; -0,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,25</t>
+          <t>-1,18; 0,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,22</t>
+          <t>-1,73; 3,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,69</t>
+          <t>-100,0; -14,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 175,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-41,49%</t>
+          <t>-24,59%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,18</t>
+          <t>-0,88; -0,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,28</t>
+          <t>-2,36; -1,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,48</t>
+          <t>-1,46; -0,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,22</t>
+          <t>-1,75; 0,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-86,05; -20,23</t>
+          <t>-84,41; -11,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-97,73; -82,0</t>
+          <t>-97,5; -80,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-82,48; -38,48</t>
+          <t>-82,98; -41,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-76,01; 12,45</t>
+          <t>-61,41; 41,76</t>
         </is>
       </c>
     </row>
